--- a/artfynd/A 41238-2025 artfynd.xlsx
+++ b/artfynd/A 41238-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,6 +1080,2733 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128987936</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90249</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>970</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bittermusseron</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucopaxillus gentianeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Quél.) Kotl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>698576</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6362932</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128987933</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>698647</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6362814</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128987938</v>
+      </c>
+      <c r="B7" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>698735</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6362825</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128987954</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90249</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>970</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bittermusseron</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leucopaxillus gentianeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Quél.) Kotl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>698667</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6362929</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128987955</v>
+      </c>
+      <c r="B9" t="n">
+        <v>86985</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>449</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>698669</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6362929</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128987942</v>
+      </c>
+      <c r="B10" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>698676</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6362855</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128987943</v>
+      </c>
+      <c r="B11" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>698651</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6362898</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128987926</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87008</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>698535</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6362865</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128981509</v>
+      </c>
+      <c r="B13" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Austerhagen, Austerhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>698738</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6362764</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128987924</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57666</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>698710</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6362749</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stort risbo i toppen på en äldre tall, troligen havsörnsbo då en havsörn kacklade i skogen omkring.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128987963</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>698684</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6362705</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128987925</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87008</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>698620</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6362922</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128987960</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>698668</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6362724</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128987929</v>
+      </c>
+      <c r="B18" t="n">
+        <v>86764</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>698651</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6362805</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128987941</v>
+      </c>
+      <c r="B19" t="n">
+        <v>86762</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörkfjällig olivspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius melanotus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>698675</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6362828</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128987956</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>698675</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6362913</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128982753</v>
+      </c>
+      <c r="B21" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Austerhagen, Austerhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>698618</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6362818</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128987928</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92810</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>698647</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6362814</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128987964</v>
+      </c>
+      <c r="B23" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>698675</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6362693</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128982066</v>
+      </c>
+      <c r="B24" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skäldan, Skäldan, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>698665</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6362903</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128987962</v>
+      </c>
+      <c r="B25" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>698678</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6362771</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128987949</v>
+      </c>
+      <c r="B26" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>698667</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6362931</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128987937</v>
+      </c>
+      <c r="B27" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>698631</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6362815</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128987927</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92810</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>698654</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6362822</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128987930</v>
+      </c>
+      <c r="B29" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>698631</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6362815</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128987940</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92798</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>698688</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6362821</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128987934</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92798</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>698528</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6362918</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128987931</v>
+      </c>
+      <c r="B32" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>698662</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6362822</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41238-2025 artfynd.xlsx
+++ b/artfynd/A 41238-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,32 +1373,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128987954</v>
+        <v>128987955</v>
       </c>
       <c r="B8" t="n">
-        <v>90249</v>
+        <v>86985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>970</v>
+        <v>449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698667</v>
+        <v>698669</v>
       </c>
       <c r="R8" t="n">
         <v>6362929</v>
@@ -1470,32 +1470,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128987955</v>
+        <v>128987942</v>
       </c>
       <c r="B9" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698669</v>
+        <v>698676</v>
       </c>
       <c r="R9" t="n">
-        <v>6362929</v>
+        <v>6362855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128987942</v>
+        <v>128987954</v>
       </c>
       <c r="B10" t="n">
-        <v>86963</v>
+        <v>90249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>970</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698676</v>
+        <v>698667</v>
       </c>
       <c r="R10" t="n">
-        <v>6362855</v>
+        <v>6362929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1858,45 +1858,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128981509</v>
+        <v>128987925</v>
       </c>
       <c r="B13" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Austerhagen, Austerhagen, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698738</v>
+        <v>698620</v>
       </c>
       <c r="R13" t="n">
-        <v>6362764</v>
+        <v>6362922</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,49 +1955,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128987924</v>
+        <v>128981509</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>86926</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100067</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Austerhagen, Austerhagen, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698710</v>
+        <v>698738</v>
       </c>
       <c r="R14" t="n">
-        <v>6362749</v>
+        <v>6362764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,11 +2026,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stort risbo i toppen på en äldre tall, troligen havsörnsbo då en havsörn kacklade i skogen omkring.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,32 +2149,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128987925</v>
+        <v>128987960</v>
       </c>
       <c r="B16" t="n">
-        <v>87008</v>
+        <v>92834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3767</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2184,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698620</v>
+        <v>698668</v>
       </c>
       <c r="R16" t="n">
-        <v>6362922</v>
+        <v>6362724</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2246,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128987960</v>
+        <v>128987929</v>
       </c>
       <c r="B17" t="n">
-        <v>92834</v>
+        <v>86764</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2266,21 +2257,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2281,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698668</v>
+        <v>698651</v>
       </c>
       <c r="R17" t="n">
-        <v>6362724</v>
+        <v>6362805</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,32 +2343,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128987929</v>
+        <v>128987941</v>
       </c>
       <c r="B18" t="n">
-        <v>86764</v>
+        <v>86762</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3762</v>
+        <v>1985</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2387,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698651</v>
+        <v>698675</v>
       </c>
       <c r="R18" t="n">
-        <v>6362805</v>
+        <v>6362828</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,32 +2440,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128987941</v>
+        <v>128987956</v>
       </c>
       <c r="B19" t="n">
-        <v>86762</v>
+        <v>92834</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1985</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,7 +2478,7 @@
         <v>698675</v>
       </c>
       <c r="R19" t="n">
-        <v>6362828</v>
+        <v>6362913</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,45 +2537,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128987956</v>
+        <v>128982753</v>
       </c>
       <c r="B20" t="n">
-        <v>92834</v>
+        <v>86963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Austerhagen, Austerhagen, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698675</v>
+        <v>698618</v>
       </c>
       <c r="R20" t="n">
-        <v>6362913</v>
+        <v>6362818</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,45 +2634,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128982753</v>
+        <v>128987928</v>
       </c>
       <c r="B21" t="n">
-        <v>86963</v>
+        <v>92810</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Austerhagen, Austerhagen, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698618</v>
+        <v>698647</v>
       </c>
       <c r="R21" t="n">
-        <v>6362818</v>
+        <v>6362814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128987928</v>
+        <v>128987964</v>
       </c>
       <c r="B22" t="n">
-        <v>92810</v>
+        <v>86926</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,21 +2742,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698647</v>
+        <v>698675</v>
       </c>
       <c r="R22" t="n">
-        <v>6362814</v>
+        <v>6362693</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,45 +2828,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128987964</v>
+        <v>128982066</v>
       </c>
       <c r="B23" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Skäldan, Skäldan, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698675</v>
+        <v>698665</v>
       </c>
       <c r="R23" t="n">
-        <v>6362693</v>
+        <v>6362903</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,7 +2925,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128982066</v>
+        <v>128987962</v>
       </c>
       <c r="B24" t="n">
         <v>86963</v>
@@ -2965,14 +2956,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skäldan, Skäldan, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698665</v>
+        <v>698678</v>
       </c>
       <c r="R24" t="n">
-        <v>6362903</v>
+        <v>6362771</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,32 +3022,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128987962</v>
+        <v>128987937</v>
       </c>
       <c r="B25" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698678</v>
+        <v>698631</v>
       </c>
       <c r="R25" t="n">
-        <v>6362771</v>
+        <v>6362815</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128987949</v>
+        <v>128987927</v>
       </c>
       <c r="B26" t="n">
-        <v>86926</v>
+        <v>92810</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,21 +3130,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3674</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698667</v>
+        <v>698654</v>
       </c>
       <c r="R26" t="n">
-        <v>6362931</v>
+        <v>6362822</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3216,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128987937</v>
+        <v>128987949</v>
       </c>
       <c r="B27" t="n">
         <v>86926</v>
@@ -3260,10 +3251,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698631</v>
+        <v>698667</v>
       </c>
       <c r="R27" t="n">
-        <v>6362815</v>
+        <v>6362931</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3322,10 +3313,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128987927</v>
+        <v>128987940</v>
       </c>
       <c r="B28" t="n">
-        <v>92810</v>
+        <v>92798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3324,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3357,10 +3348,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698654</v>
+        <v>698688</v>
       </c>
       <c r="R28" t="n">
-        <v>6362822</v>
+        <v>6362821</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,7 +3508,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128987940</v>
+        <v>128987934</v>
       </c>
       <c r="B30" t="n">
         <v>92798</v>
@@ -3552,10 +3543,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>698688</v>
+        <v>698528</v>
       </c>
       <c r="R30" t="n">
-        <v>6362821</v>
+        <v>6362918</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3614,32 +3605,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128987934</v>
+        <v>128987931</v>
       </c>
       <c r="B31" t="n">
-        <v>92798</v>
+        <v>86963</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6003295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3649,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>698528</v>
+        <v>698662</v>
       </c>
       <c r="R31" t="n">
-        <v>6362918</v>
+        <v>6362822</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,6 +3684,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3711,7 +3703,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128987931</v>
+        <v>128994128</v>
       </c>
       <c r="B32" t="n">
         <v>86963</v>
@@ -3742,14 +3734,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Hajdes, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>698662</v>
+        <v>698621</v>
       </c>
       <c r="R32" t="n">
-        <v>6362822</v>
+        <v>6362788</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3797,15 +3789,1495 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128994130</v>
+      </c>
+      <c r="B33" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>698584</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6362959</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128994140</v>
+      </c>
+      <c r="B34" t="n">
+        <v>86985</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>449</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>698664</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6362939</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>mikroskoperad: 14-15x7-8 mikrometer</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128994131</v>
+      </c>
+      <c r="B35" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>698666</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6362926</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128994129</v>
+      </c>
+      <c r="B36" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>698515</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6362883</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128994132</v>
+      </c>
+      <c r="B37" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>698729</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6362799</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128994148</v>
+      </c>
+      <c r="B38" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>698563</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6362937</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128994134</v>
+      </c>
+      <c r="B39" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>698731</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6362798</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128994150</v>
+      </c>
+      <c r="B40" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>698631</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6362945</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128994149</v>
+      </c>
+      <c r="B41" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>698555</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6362962</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128994133</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>698737</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6362793</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128994153</v>
+      </c>
+      <c r="B43" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>698756</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6362753</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128994154</v>
+      </c>
+      <c r="B44" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>698808</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6362755</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128994136</v>
+      </c>
+      <c r="B45" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>698802</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6362738</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128994135</v>
+      </c>
+      <c r="B46" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>698746</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6362793</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128994152</v>
+      </c>
+      <c r="B47" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hajdes, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>698748</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6362792</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41238-2025 artfynd.xlsx
+++ b/artfynd/A 41238-2025 artfynd.xlsx
@@ -1085,7 +1085,7 @@
         <v>128987936</v>
       </c>
       <c r="B5" t="n">
-        <v>90249</v>
+        <v>90254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>128987933</v>
       </c>
       <c r="B6" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>128987938</v>
       </c>
       <c r="B7" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,32 +1373,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128987955</v>
+        <v>128987954</v>
       </c>
       <c r="B8" t="n">
-        <v>86985</v>
+        <v>90254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>449</v>
+        <v>970</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698669</v>
+        <v>698667</v>
       </c>
       <c r="R8" t="n">
         <v>6362929</v>
@@ -1470,32 +1470,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128987942</v>
+        <v>128987955</v>
       </c>
       <c r="B9" t="n">
-        <v>86963</v>
+        <v>86990</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698676</v>
+        <v>698669</v>
       </c>
       <c r="R9" t="n">
-        <v>6362855</v>
+        <v>6362929</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128987954</v>
+        <v>128987942</v>
       </c>
       <c r="B10" t="n">
-        <v>90249</v>
+        <v>86968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698667</v>
+        <v>698676</v>
       </c>
       <c r="R10" t="n">
-        <v>6362929</v>
+        <v>6362855</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1667,7 @@
         <v>128987943</v>
       </c>
       <c r="B11" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128987926</v>
       </c>
       <c r="B12" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,32 +1858,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128987925</v>
+        <v>128987963</v>
       </c>
       <c r="B13" t="n">
-        <v>87008</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3767</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698620</v>
+        <v>698684</v>
       </c>
       <c r="R13" t="n">
-        <v>6362922</v>
+        <v>6362705</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,7 +1958,7 @@
         <v>128981509</v>
       </c>
       <c r="B14" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128987963</v>
+        <v>128987925</v>
       </c>
       <c r="B15" t="n">
-        <v>91528</v>
+        <v>87013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>3767</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698684</v>
+        <v>698620</v>
       </c>
       <c r="R15" t="n">
-        <v>6362705</v>
+        <v>6362922</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
         <v>128987960</v>
       </c>
       <c r="B16" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>128987929</v>
       </c>
       <c r="B17" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>128987941</v>
       </c>
       <c r="B18" t="n">
-        <v>86762</v>
+        <v>86767</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128987956</v>
       </c>
       <c r="B19" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,45 +2537,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128982753</v>
+        <v>128987928</v>
       </c>
       <c r="B20" t="n">
-        <v>86963</v>
+        <v>92815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Austerhagen, Austerhagen, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698618</v>
+        <v>698647</v>
       </c>
       <c r="R20" t="n">
-        <v>6362818</v>
+        <v>6362814</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,45 +2634,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128987928</v>
+        <v>128982753</v>
       </c>
       <c r="B21" t="n">
-        <v>92810</v>
+        <v>86968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Austerhagen, Austerhagen, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698647</v>
+        <v>698618</v>
       </c>
       <c r="R21" t="n">
-        <v>6362814</v>
+        <v>6362818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
         <v>128987964</v>
       </c>
       <c r="B22" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2828,45 +2828,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128982066</v>
+        <v>128987927</v>
       </c>
       <c r="B23" t="n">
-        <v>86963</v>
+        <v>92815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skäldan, Skäldan, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698665</v>
+        <v>698654</v>
       </c>
       <c r="R23" t="n">
-        <v>6362903</v>
+        <v>6362822</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128987962</v>
+        <v>128987937</v>
       </c>
       <c r="B24" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698678</v>
+        <v>698631</v>
       </c>
       <c r="R24" t="n">
-        <v>6362771</v>
+        <v>6362815</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128987937</v>
+        <v>128987949</v>
       </c>
       <c r="B25" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698631</v>
+        <v>698667</v>
       </c>
       <c r="R25" t="n">
-        <v>6362815</v>
+        <v>6362931</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,45 +3119,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128987927</v>
+        <v>128982066</v>
       </c>
       <c r="B26" t="n">
-        <v>92810</v>
+        <v>86968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Skäldan, Skäldan, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698654</v>
+        <v>698665</v>
       </c>
       <c r="R26" t="n">
-        <v>6362822</v>
+        <v>6362903</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,32 +3216,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128987949</v>
+        <v>128987962</v>
       </c>
       <c r="B27" t="n">
-        <v>86926</v>
+        <v>86968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698667</v>
+        <v>698678</v>
       </c>
       <c r="R27" t="n">
-        <v>6362931</v>
+        <v>6362771</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3313,32 +3313,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128987940</v>
+        <v>128987930</v>
       </c>
       <c r="B28" t="n">
-        <v>92798</v>
+        <v>86968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698688</v>
+        <v>698631</v>
       </c>
       <c r="R28" t="n">
-        <v>6362821</v>
+        <v>6362815</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,6 +3392,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3410,32 +3411,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128987930</v>
+        <v>128987940</v>
       </c>
       <c r="B29" t="n">
-        <v>86963</v>
+        <v>92803</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6003295</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3445,10 +3446,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698631</v>
+        <v>698688</v>
       </c>
       <c r="R29" t="n">
-        <v>6362815</v>
+        <v>6362821</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3489,7 +3490,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>128987934</v>
       </c>
       <c r="B30" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>128987931</v>
       </c>
       <c r="B31" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128994128</v>
+        <v>128994130</v>
       </c>
       <c r="B32" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>698621</v>
+        <v>698584</v>
       </c>
       <c r="R32" t="n">
-        <v>6362788</v>
+        <v>6362959</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3801,10 +3801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128994130</v>
+        <v>128994128</v>
       </c>
       <c r="B33" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>698584</v>
+        <v>698621</v>
       </c>
       <c r="R33" t="n">
-        <v>6362959</v>
+        <v>6362788</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
         <v>128994140</v>
       </c>
       <c r="B34" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>128994131</v>
       </c>
       <c r="B35" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>128994129</v>
       </c>
       <c r="B36" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>128994132</v>
       </c>
       <c r="B37" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>128994148</v>
       </c>
       <c r="B38" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>128994134</v>
       </c>
       <c r="B39" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>128994150</v>
       </c>
       <c r="B40" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>128994149</v>
       </c>
       <c r="B41" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4696,32 +4696,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128994133</v>
+        <v>128994153</v>
       </c>
       <c r="B42" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>698737</v>
+        <v>698756</v>
       </c>
       <c r="R42" t="n">
-        <v>6362793</v>
+        <v>6362753</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4775,7 +4775,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4794,32 +4793,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128994153</v>
+        <v>128994133</v>
       </c>
       <c r="B43" t="n">
-        <v>86926</v>
+        <v>86968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4828,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>698756</v>
+        <v>698737</v>
       </c>
       <c r="R43" t="n">
-        <v>6362753</v>
+        <v>6362793</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4873,6 +4872,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>128994154</v>
       </c>
       <c r="B44" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>128994136</v>
       </c>
       <c r="B45" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>128994135</v>
       </c>
       <c r="B46" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>128994152</v>
       </c>
       <c r="B47" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 41238-2025 artfynd.xlsx
+++ b/artfynd/A 41238-2025 artfynd.xlsx
@@ -1179,32 +1179,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128987938</v>
+        <v>128987933</v>
       </c>
       <c r="B6" t="n">
-        <v>86975</v>
+        <v>92847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698735</v>
+        <v>698647</v>
       </c>
       <c r="R6" t="n">
-        <v>6362825</v>
+        <v>6362814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128987933</v>
+        <v>128987938</v>
       </c>
       <c r="B7" t="n">
-        <v>92847</v>
+        <v>86975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698647</v>
+        <v>698735</v>
       </c>
       <c r="R7" t="n">
-        <v>6362814</v>
+        <v>6362825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1470,32 +1470,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128987955</v>
+        <v>128987942</v>
       </c>
       <c r="B9" t="n">
-        <v>86997</v>
+        <v>86975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698669</v>
+        <v>698676</v>
       </c>
       <c r="R9" t="n">
-        <v>6362929</v>
+        <v>6362855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128987942</v>
+        <v>128987955</v>
       </c>
       <c r="B10" t="n">
-        <v>86975</v>
+        <v>86997</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698676</v>
+        <v>698669</v>
       </c>
       <c r="R10" t="n">
-        <v>6362855</v>
+        <v>6362929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2828,45 +2828,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128982066</v>
+        <v>128987927</v>
       </c>
       <c r="B23" t="n">
-        <v>86975</v>
+        <v>92823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skäldan, Skäldan, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698665</v>
+        <v>698654</v>
       </c>
       <c r="R23" t="n">
-        <v>6362903</v>
+        <v>6362822</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128987962</v>
+        <v>128987949</v>
       </c>
       <c r="B24" t="n">
-        <v>86975</v>
+        <v>86938</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698678</v>
+        <v>698667</v>
       </c>
       <c r="R24" t="n">
-        <v>6362771</v>
+        <v>6362931</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,45 +3022,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128987937</v>
+        <v>128982066</v>
       </c>
       <c r="B25" t="n">
-        <v>86938</v>
+        <v>86975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Skäldan, Skäldan, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698631</v>
+        <v>698665</v>
       </c>
       <c r="R25" t="n">
-        <v>6362815</v>
+        <v>6362903</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,32 +3119,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128987927</v>
+        <v>128987962</v>
       </c>
       <c r="B26" t="n">
-        <v>92823</v>
+        <v>86975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698654</v>
+        <v>698678</v>
       </c>
       <c r="R26" t="n">
-        <v>6362822</v>
+        <v>6362771</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128987949</v>
+        <v>128987937</v>
       </c>
       <c r="B27" t="n">
         <v>86938</v>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698667</v>
+        <v>698631</v>
       </c>
       <c r="R27" t="n">
-        <v>6362931</v>
+        <v>6362815</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3313,32 +3313,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128987930</v>
+        <v>128987940</v>
       </c>
       <c r="B28" t="n">
-        <v>86975</v>
+        <v>92811</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698631</v>
+        <v>698688</v>
       </c>
       <c r="R28" t="n">
-        <v>6362815</v>
+        <v>6362821</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,7 +3392,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3411,32 +3410,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128987940</v>
+        <v>128987930</v>
       </c>
       <c r="B29" t="n">
-        <v>92811</v>
+        <v>86975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6003295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3446,10 +3445,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698688</v>
+        <v>698631</v>
       </c>
       <c r="R29" t="n">
-        <v>6362821</v>
+        <v>6362815</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3490,6 +3489,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41238-2025 artfynd.xlsx
+++ b/artfynd/A 41238-2025 artfynd.xlsx
@@ -1085,7 +1085,7 @@
         <v>128987936</v>
       </c>
       <c r="B5" t="n">
-        <v>90261</v>
+        <v>90264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,32 +1179,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128987933</v>
+        <v>128987938</v>
       </c>
       <c r="B6" t="n">
-        <v>92847</v>
+        <v>86978</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698647</v>
+        <v>698735</v>
       </c>
       <c r="R6" t="n">
-        <v>6362814</v>
+        <v>6362825</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128987938</v>
+        <v>128987933</v>
       </c>
       <c r="B7" t="n">
-        <v>86975</v>
+        <v>92852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698735</v>
+        <v>698647</v>
       </c>
       <c r="R7" t="n">
-        <v>6362825</v>
+        <v>6362814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128987954</v>
+        <v>128987942</v>
       </c>
       <c r="B8" t="n">
-        <v>90261</v>
+        <v>86978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698667</v>
+        <v>698676</v>
       </c>
       <c r="R8" t="n">
-        <v>6362929</v>
+        <v>6362855</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,32 +1470,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128987942</v>
+        <v>128987955</v>
       </c>
       <c r="B9" t="n">
-        <v>86975</v>
+        <v>87000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698676</v>
+        <v>698669</v>
       </c>
       <c r="R9" t="n">
-        <v>6362855</v>
+        <v>6362929</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128987955</v>
+        <v>128987954</v>
       </c>
       <c r="B10" t="n">
-        <v>86997</v>
+        <v>90264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>449</v>
+        <v>970</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698669</v>
+        <v>698667</v>
       </c>
       <c r="R10" t="n">
         <v>6362929</v>
@@ -1667,7 +1667,7 @@
         <v>128987943</v>
       </c>
       <c r="B11" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128987926</v>
       </c>
       <c r="B12" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>128987925</v>
       </c>
       <c r="B13" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,45 +1955,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128987963</v>
+        <v>128981509</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>86941</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Austerhagen, Austerhagen, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698684</v>
+        <v>698738</v>
       </c>
       <c r="R14" t="n">
-        <v>6362705</v>
+        <v>6362764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,45 +2052,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128981509</v>
+        <v>128987963</v>
       </c>
       <c r="B15" t="n">
-        <v>86938</v>
+        <v>91543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Austerhagen, Austerhagen, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698738</v>
+        <v>698684</v>
       </c>
       <c r="R15" t="n">
-        <v>6362764</v>
+        <v>6362705</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
         <v>128987960</v>
       </c>
       <c r="B16" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>128987929</v>
       </c>
       <c r="B17" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>128987956</v>
       </c>
       <c r="B18" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128987941</v>
       </c>
       <c r="B19" t="n">
-        <v>86774</v>
+        <v>86777</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,45 +2537,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128982753</v>
+        <v>128987928</v>
       </c>
       <c r="B20" t="n">
-        <v>86975</v>
+        <v>92828</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Austerhagen, Austerhagen, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698618</v>
+        <v>698647</v>
       </c>
       <c r="R20" t="n">
-        <v>6362818</v>
+        <v>6362814</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,45 +2634,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128987928</v>
+        <v>128982753</v>
       </c>
       <c r="B21" t="n">
-        <v>92823</v>
+        <v>86978</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Austerhagen, Austerhagen, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698647</v>
+        <v>698618</v>
       </c>
       <c r="R21" t="n">
-        <v>6362814</v>
+        <v>6362818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
         <v>128987964</v>
       </c>
       <c r="B22" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>128987927</v>
       </c>
       <c r="B23" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>128987949</v>
       </c>
       <c r="B24" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3022,45 +3022,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128982066</v>
+        <v>128987937</v>
       </c>
       <c r="B25" t="n">
-        <v>86975</v>
+        <v>86941</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skäldan, Skäldan, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698665</v>
+        <v>698631</v>
       </c>
       <c r="R25" t="n">
-        <v>6362903</v>
+        <v>6362815</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128987962</v>
+        <v>128982066</v>
       </c>
       <c r="B26" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,14 +3150,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Skäldan, Skäldan, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698678</v>
+        <v>698665</v>
       </c>
       <c r="R26" t="n">
-        <v>6362771</v>
+        <v>6362903</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,32 +3216,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128987937</v>
+        <v>128987962</v>
       </c>
       <c r="B27" t="n">
-        <v>86938</v>
+        <v>86978</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698631</v>
+        <v>698678</v>
       </c>
       <c r="R27" t="n">
-        <v>6362815</v>
+        <v>6362771</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3313,32 +3313,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128987940</v>
+        <v>128987930</v>
       </c>
       <c r="B28" t="n">
-        <v>92811</v>
+        <v>86978</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698688</v>
+        <v>698631</v>
       </c>
       <c r="R28" t="n">
-        <v>6362821</v>
+        <v>6362815</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,6 +3392,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3410,32 +3411,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128987930</v>
+        <v>128987940</v>
       </c>
       <c r="B29" t="n">
-        <v>86975</v>
+        <v>92816</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6003295</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3445,10 +3446,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698631</v>
+        <v>698688</v>
       </c>
       <c r="R29" t="n">
-        <v>6362815</v>
+        <v>6362821</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3489,7 +3490,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>128987934</v>
       </c>
       <c r="B30" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>128987931</v>
       </c>
       <c r="B31" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>128994128</v>
       </c>
       <c r="B32" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>128994130</v>
       </c>
       <c r="B33" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>128994140</v>
       </c>
       <c r="B34" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>128994131</v>
       </c>
       <c r="B35" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>128994129</v>
       </c>
       <c r="B36" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4209,32 +4209,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994148</v>
+        <v>128994132</v>
       </c>
       <c r="B37" t="n">
-        <v>86938</v>
+        <v>86978</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>698563</v>
+        <v>698729</v>
       </c>
       <c r="R37" t="n">
-        <v>6362937</v>
+        <v>6362799</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4288,6 +4288,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4306,32 +4307,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994132</v>
+        <v>128994148</v>
       </c>
       <c r="B38" t="n">
-        <v>86975</v>
+        <v>86941</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4341,10 +4342,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>698729</v>
+        <v>698563</v>
       </c>
       <c r="R38" t="n">
-        <v>6362799</v>
+        <v>6362937</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4385,7 +4386,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4404,32 +4404,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128994134</v>
+        <v>128994150</v>
       </c>
       <c r="B39" t="n">
-        <v>86975</v>
+        <v>86941</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>698731</v>
+        <v>698631</v>
       </c>
       <c r="R39" t="n">
-        <v>6362798</v>
+        <v>6362945</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,7 +4483,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4502,32 +4501,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128994150</v>
+        <v>128994134</v>
       </c>
       <c r="B40" t="n">
-        <v>86938</v>
+        <v>86978</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4537,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>698631</v>
+        <v>698731</v>
       </c>
       <c r="R40" t="n">
-        <v>6362945</v>
+        <v>6362798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4581,6 +4580,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>128994149</v>
       </c>
       <c r="B41" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128994153</v>
+        <v>128994154</v>
       </c>
       <c r="B42" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>698756</v>
+        <v>698808</v>
       </c>
       <c r="R42" t="n">
-        <v>6362753</v>
+        <v>6362755</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128994154</v>
+        <v>128994153</v>
       </c>
       <c r="B43" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>698808</v>
+        <v>698756</v>
       </c>
       <c r="R43" t="n">
-        <v>6362755</v>
+        <v>6362753</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,7 +4893,7 @@
         <v>128994133</v>
       </c>
       <c r="B44" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>128994136</v>
       </c>
       <c r="B45" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>128994135</v>
       </c>
       <c r="B46" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>128994152</v>
       </c>
       <c r="B47" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 41238-2025 artfynd.xlsx
+++ b/artfynd/A 41238-2025 artfynd.xlsx
@@ -1085,7 +1085,7 @@
         <v>128987936</v>
       </c>
       <c r="B5" t="n">
-        <v>90264</v>
+        <v>90267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>128987938</v>
       </c>
       <c r="B6" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>128987933</v>
       </c>
       <c r="B7" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128987942</v>
+        <v>128987954</v>
       </c>
       <c r="B8" t="n">
-        <v>86978</v>
+        <v>90267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>970</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698676</v>
+        <v>698667</v>
       </c>
       <c r="R8" t="n">
-        <v>6362855</v>
+        <v>6362929</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
         <v>128987955</v>
       </c>
       <c r="B9" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128987954</v>
+        <v>128987942</v>
       </c>
       <c r="B10" t="n">
-        <v>90264</v>
+        <v>86981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698667</v>
+        <v>698676</v>
       </c>
       <c r="R10" t="n">
-        <v>6362929</v>
+        <v>6362855</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1667,7 @@
         <v>128987943</v>
       </c>
       <c r="B11" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128987926</v>
       </c>
       <c r="B12" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,32 +1858,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128987925</v>
+        <v>128987963</v>
       </c>
       <c r="B13" t="n">
-        <v>87023</v>
+        <v>91546</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3767</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698620</v>
+        <v>698684</v>
       </c>
       <c r="R13" t="n">
-        <v>6362922</v>
+        <v>6362705</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,45 +1955,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128981509</v>
+        <v>128987925</v>
       </c>
       <c r="B14" t="n">
-        <v>86941</v>
+        <v>87026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Austerhagen, Austerhagen, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698738</v>
+        <v>698620</v>
       </c>
       <c r="R14" t="n">
-        <v>6362764</v>
+        <v>6362922</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,45 +2052,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128987963</v>
+        <v>128981509</v>
       </c>
       <c r="B15" t="n">
-        <v>91543</v>
+        <v>86944</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Austerhagen, Austerhagen, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698684</v>
+        <v>698738</v>
       </c>
       <c r="R15" t="n">
-        <v>6362705</v>
+        <v>6362764</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
         <v>128987960</v>
       </c>
       <c r="B16" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>128987929</v>
       </c>
       <c r="B17" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,32 +2343,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128987956</v>
+        <v>128987941</v>
       </c>
       <c r="B18" t="n">
-        <v>92852</v>
+        <v>86780</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>1985</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2381,7 +2381,7 @@
         <v>698675</v>
       </c>
       <c r="R18" t="n">
-        <v>6362913</v>
+        <v>6362828</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,32 +2440,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128987941</v>
+        <v>128987956</v>
       </c>
       <c r="B19" t="n">
-        <v>86777</v>
+        <v>92855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1985</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
         <v>698675</v>
       </c>
       <c r="R19" t="n">
-        <v>6362828</v>
+        <v>6362913</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,7 +2540,7 @@
         <v>128987928</v>
       </c>
       <c r="B20" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>128982753</v>
       </c>
       <c r="B21" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>128987964</v>
       </c>
       <c r="B22" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128987927</v>
+        <v>128987937</v>
       </c>
       <c r="B23" t="n">
-        <v>92828</v>
+        <v>86944</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698654</v>
+        <v>698631</v>
       </c>
       <c r="R23" t="n">
-        <v>6362822</v>
+        <v>6362815</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128987949</v>
+        <v>128987927</v>
       </c>
       <c r="B24" t="n">
-        <v>86941</v>
+        <v>92831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3674</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698667</v>
+        <v>698654</v>
       </c>
       <c r="R24" t="n">
-        <v>6362931</v>
+        <v>6362822</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128987937</v>
+        <v>128987949</v>
       </c>
       <c r="B25" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698631</v>
+        <v>698667</v>
       </c>
       <c r="R25" t="n">
-        <v>6362815</v>
+        <v>6362931</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
         <v>128982066</v>
       </c>
       <c r="B26" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>128987962</v>
       </c>
       <c r="B27" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3313,32 +3313,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128987930</v>
+        <v>128987940</v>
       </c>
       <c r="B28" t="n">
-        <v>86978</v>
+        <v>92819</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698631</v>
+        <v>698688</v>
       </c>
       <c r="R28" t="n">
-        <v>6362815</v>
+        <v>6362821</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,7 +3392,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3411,32 +3410,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128987940</v>
+        <v>128987930</v>
       </c>
       <c r="B29" t="n">
-        <v>92816</v>
+        <v>86981</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6003295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3446,10 +3445,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698688</v>
+        <v>698631</v>
       </c>
       <c r="R29" t="n">
-        <v>6362821</v>
+        <v>6362815</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3490,6 +3489,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>128987934</v>
       </c>
       <c r="B30" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>128987931</v>
       </c>
       <c r="B31" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>128994128</v>
       </c>
       <c r="B32" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>128994130</v>
       </c>
       <c r="B33" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>128994140</v>
       </c>
       <c r="B34" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>128994131</v>
       </c>
       <c r="B35" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>128994129</v>
       </c>
       <c r="B36" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4209,32 +4209,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994132</v>
+        <v>128994148</v>
       </c>
       <c r="B37" t="n">
-        <v>86978</v>
+        <v>86944</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>698729</v>
+        <v>698563</v>
       </c>
       <c r="R37" t="n">
-        <v>6362799</v>
+        <v>6362937</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4288,7 +4288,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4307,32 +4306,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994148</v>
+        <v>128994132</v>
       </c>
       <c r="B38" t="n">
-        <v>86941</v>
+        <v>86981</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4342,10 +4341,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>698563</v>
+        <v>698729</v>
       </c>
       <c r="R38" t="n">
-        <v>6362937</v>
+        <v>6362799</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4386,6 +4385,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>128994150</v>
       </c>
       <c r="B39" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>128994134</v>
       </c>
       <c r="B40" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>128994149</v>
       </c>
       <c r="B41" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128994154</v>
+        <v>128994153</v>
       </c>
       <c r="B42" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>698808</v>
+        <v>698756</v>
       </c>
       <c r="R42" t="n">
-        <v>6362755</v>
+        <v>6362753</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128994153</v>
+        <v>128994154</v>
       </c>
       <c r="B43" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>698756</v>
+        <v>698808</v>
       </c>
       <c r="R43" t="n">
-        <v>6362753</v>
+        <v>6362755</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,7 +4893,7 @@
         <v>128994133</v>
       </c>
       <c r="B44" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>128994136</v>
       </c>
       <c r="B45" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>128994135</v>
       </c>
       <c r="B46" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>128994152</v>
       </c>
       <c r="B47" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 41238-2025 artfynd.xlsx
+++ b/artfynd/A 41238-2025 artfynd.xlsx
@@ -1179,32 +1179,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128987938</v>
+        <v>128987933</v>
       </c>
       <c r="B6" t="n">
-        <v>86981</v>
+        <v>92855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698735</v>
+        <v>698647</v>
       </c>
       <c r="R6" t="n">
-        <v>6362825</v>
+        <v>6362814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128987933</v>
+        <v>128987938</v>
       </c>
       <c r="B7" t="n">
-        <v>92855</v>
+        <v>86981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698647</v>
+        <v>698735</v>
       </c>
       <c r="R7" t="n">
-        <v>6362814</v>
+        <v>6362825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,32 +1373,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128987954</v>
+        <v>128987955</v>
       </c>
       <c r="B8" t="n">
-        <v>90267</v>
+        <v>87003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>970</v>
+        <v>449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698667</v>
+        <v>698669</v>
       </c>
       <c r="R8" t="n">
         <v>6362929</v>
@@ -1470,32 +1470,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128987955</v>
+        <v>128987954</v>
       </c>
       <c r="B9" t="n">
-        <v>87003</v>
+        <v>90267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>970</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698669</v>
+        <v>698667</v>
       </c>
       <c r="R9" t="n">
         <v>6362929</v>
@@ -2925,45 +2925,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128987927</v>
+        <v>128982066</v>
       </c>
       <c r="B24" t="n">
-        <v>92831</v>
+        <v>86981</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Skäldan, Skäldan, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698654</v>
+        <v>698665</v>
       </c>
       <c r="R24" t="n">
-        <v>6362822</v>
+        <v>6362903</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128987949</v>
+        <v>128987962</v>
       </c>
       <c r="B25" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698667</v>
+        <v>698678</v>
       </c>
       <c r="R25" t="n">
-        <v>6362931</v>
+        <v>6362771</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,45 +3119,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982066</v>
+        <v>128987949</v>
       </c>
       <c r="B26" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skäldan, Skäldan, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698665</v>
+        <v>698667</v>
       </c>
       <c r="R26" t="n">
-        <v>6362903</v>
+        <v>6362931</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,32 +3216,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128987962</v>
+        <v>128987927</v>
       </c>
       <c r="B27" t="n">
-        <v>86981</v>
+        <v>92831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698678</v>
+        <v>698654</v>
       </c>
       <c r="R27" t="n">
-        <v>6362771</v>
+        <v>6362822</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4209,32 +4209,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994148</v>
+        <v>128994132</v>
       </c>
       <c r="B37" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>698563</v>
+        <v>698729</v>
       </c>
       <c r="R37" t="n">
-        <v>6362937</v>
+        <v>6362799</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4288,6 +4288,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4306,32 +4307,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994132</v>
+        <v>128994148</v>
       </c>
       <c r="B38" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4341,10 +4342,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>698729</v>
+        <v>698563</v>
       </c>
       <c r="R38" t="n">
-        <v>6362799</v>
+        <v>6362937</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4385,7 +4386,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4696,7 +4696,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128994153</v>
+        <v>128994154</v>
       </c>
       <c r="B42" t="n">
         <v>86944</v>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>698756</v>
+        <v>698808</v>
       </c>
       <c r="R42" t="n">
-        <v>6362753</v>
+        <v>6362755</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128994154</v>
+        <v>128994153</v>
       </c>
       <c r="B43" t="n">
         <v>86944</v>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>698808</v>
+        <v>698756</v>
       </c>
       <c r="R43" t="n">
-        <v>6362755</v>
+        <v>6362753</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 41238-2025 artfynd.xlsx
+++ b/artfynd/A 41238-2025 artfynd.xlsx
@@ -1858,32 +1858,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128987963</v>
+        <v>128987925</v>
       </c>
       <c r="B13" t="n">
-        <v>91546</v>
+        <v>87026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>3767</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698684</v>
+        <v>698620</v>
       </c>
       <c r="R13" t="n">
-        <v>6362705</v>
+        <v>6362922</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,45 +1955,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128987925</v>
+        <v>128981509</v>
       </c>
       <c r="B14" t="n">
-        <v>87026</v>
+        <v>86944</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:4, Gtl</t>
+          <t>Austerhagen, Austerhagen, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698620</v>
+        <v>698738</v>
       </c>
       <c r="R14" t="n">
-        <v>6362922</v>
+        <v>6362764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,45 +2052,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128981509</v>
+        <v>128987963</v>
       </c>
       <c r="B15" t="n">
-        <v>86944</v>
+        <v>91546</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Austerhagen, Austerhagen, Gtl</t>
+          <t>Klinte Hunninge 1:4, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698738</v>
+        <v>698684</v>
       </c>
       <c r="R15" t="n">
-        <v>6362764</v>
+        <v>6362705</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -4209,32 +4209,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128994132</v>
+        <v>128994148</v>
       </c>
       <c r="B37" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>698729</v>
+        <v>698563</v>
       </c>
       <c r="R37" t="n">
-        <v>6362799</v>
+        <v>6362937</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4288,7 +4288,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4307,32 +4306,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128994148</v>
+        <v>128994132</v>
       </c>
       <c r="B38" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4342,10 +4341,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>698563</v>
+        <v>698729</v>
       </c>
       <c r="R38" t="n">
-        <v>6362937</v>
+        <v>6362799</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4386,6 +4385,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4404,32 +4404,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128994150</v>
+        <v>128994134</v>
       </c>
       <c r="B39" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>698631</v>
+        <v>698731</v>
       </c>
       <c r="R39" t="n">
-        <v>6362945</v>
+        <v>6362798</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,6 +4483,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4501,32 +4502,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128994134</v>
+        <v>128994150</v>
       </c>
       <c r="B40" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4537,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>698731</v>
+        <v>698631</v>
       </c>
       <c r="R40" t="n">
-        <v>6362798</v>
+        <v>6362945</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,7 +4581,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
